--- a/src/main/resources/templates/_tablelist/DataBaseExcel.xlsx
+++ b/src/main/resources/templates/_tablelist/DataBaseExcel.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\JAVA\SOURCE\haccpwork\workspace\kymes\src\main\resources\templates\_tablelist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\aprjKYMES\src\main\resources\templates\_tablelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0685899-7DB8-48E2-9FFF-46833CBA5E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="690">
   <si>
     <t>테이블명</t>
   </si>
@@ -963,9 +967,6 @@
     <t>subpartnm</t>
   </si>
   <si>
-    <t>사출정보</t>
-  </si>
-  <si>
     <t>생산계획번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -982,6 +983,176 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>불량수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사로트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차검사수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차검사수량</t>
+  </si>
+  <si>
+    <t>3차검사수량</t>
+  </si>
+  <si>
+    <t>4차검사수량</t>
+  </si>
+  <si>
+    <t>5차검사수량</t>
+  </si>
+  <si>
+    <t>6차검사수량</t>
+  </si>
+  <si>
+    <t>7차검사수량</t>
+  </si>
+  <si>
+    <t>부자재코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부자재명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TB_FPLAN_W020</t>
+  </si>
+  <si>
+    <t>wsumqt</t>
+  </si>
+  <si>
+    <t>wboxsu</t>
+  </si>
+  <si>
+    <t>wcode</t>
+  </si>
+  <si>
+    <t>검사로트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생산계획번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사시작일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사종료일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사량2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업자코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록자코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적입수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>품목코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>픔목코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TB_FPLAN_WBAD</t>
+  </si>
+  <si>
+    <t>wbqty</t>
+  </si>
+  <si>
+    <t>불량정보</t>
+  </si>
+  <si>
+    <t>로트번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불량코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TB_FPLAN_WORK</t>
+  </si>
+  <si>
+    <t>varchar(6)</t>
+  </si>
+  <si>
+    <t>wstdt</t>
+  </si>
+  <si>
+    <t>wendt</t>
+  </si>
+  <si>
+    <t>wtable</t>
+  </si>
+  <si>
+    <t>생산작업정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생산계획번호2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업종료일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생산시작시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생산종료시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>완료량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -994,113 +1165,579 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>공정테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>작업자코드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>등록일자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>생산계획번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TB_FPLAN_WTIME</t>
+  </si>
+  <si>
+    <t>seq</t>
+  </si>
+  <si>
+    <t>wopdv</t>
+  </si>
+  <si>
+    <t>wrerm</t>
+  </si>
+  <si>
+    <t>aseq</t>
+  </si>
+  <si>
+    <t>가동비가동정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세순번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업시작시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업중지시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비가동코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비가동사유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생산계획번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TB_PC110</t>
+  </si>
+  <si>
+    <t>machcd</t>
+  </si>
+  <si>
+    <t>machno</t>
+  </si>
+  <si>
+    <t>machname</t>
+  </si>
+  <si>
+    <t>machdate</t>
+  </si>
+  <si>
+    <t>machstdate</t>
+  </si>
+  <si>
+    <t>macheddate</t>
+  </si>
+  <si>
+    <t>machshot</t>
+  </si>
+  <si>
+    <t>machgugek03</t>
+  </si>
+  <si>
+    <t>machgugek02</t>
+  </si>
+  <si>
+    <t>machgugek01</t>
+  </si>
+  <si>
+    <t>machcavity</t>
+  </si>
+  <si>
+    <t>machuse</t>
+  </si>
+  <si>
+    <t>machcha</t>
+  </si>
+  <si>
+    <t>machjaejak</t>
+  </si>
+  <si>
+    <t>machcltcd</t>
+  </si>
+  <si>
+    <t>machcltnm</t>
+  </si>
+  <si>
+    <t>machplace</t>
+  </si>
+  <si>
+    <t>machamt</t>
+  </si>
+  <si>
+    <t>machwon</t>
+  </si>
+  <si>
+    <t>machgrade</t>
+  </si>
+  <si>
+    <t>machgram</t>
+  </si>
+  <si>
+    <t>machncha</t>
+  </si>
+  <si>
+    <t>machnum</t>
+  </si>
+  <si>
+    <t>inpcode</t>
+  </si>
+  <si>
+    <t>injpum</t>
+  </si>
+  <si>
+    <t>machgumnm</t>
+  </si>
+  <si>
+    <t>금형정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>품번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금형번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최초입고일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제작시작일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제작종료일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수명예상SHOT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금형규격03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금형규격02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAVITY수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용기계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>차종(모델명)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금형제작업체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금형보관위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원재료명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금형등급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제품중량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N차금형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>등록자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>투입원자재코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사로트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1차검사수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차검사수량</t>
-  </si>
-  <si>
-    <t>3차검사수량</t>
-  </si>
-  <si>
-    <t>4차검사수량</t>
-  </si>
-  <si>
-    <t>5차검사수량</t>
-  </si>
-  <si>
-    <t>6차검사수량</t>
-  </si>
-  <si>
-    <t>7차검사수량</t>
-  </si>
-  <si>
-    <t>원자재명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부자재코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부자재명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TB_FPLAN_W020</t>
-  </si>
-  <si>
-    <t>wsumqt</t>
-  </si>
-  <si>
-    <t>wboxsu</t>
-  </si>
-  <si>
-    <t>wcode</t>
-  </si>
-  <si>
-    <t>검사정보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사로트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생산계획번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사시작일자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사종료일자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설비코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사량2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>누적수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업자코드</t>
+    <t>품명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금형명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jcode</t>
+  </si>
+  <si>
+    <t>jkey</t>
+  </si>
+  <si>
+    <t>nvarchar(20)</t>
+  </si>
+  <si>
+    <t>j_dae</t>
+  </si>
+  <si>
+    <t>nvarchar(4)</t>
+  </si>
+  <si>
+    <t>j_jung</t>
+  </si>
+  <si>
+    <t>nvarchar(8)</t>
+  </si>
+  <si>
+    <t>jpum</t>
+  </si>
+  <si>
+    <t>nvarchar(80)</t>
+  </si>
+  <si>
+    <t>jgugek</t>
+  </si>
+  <si>
+    <t>nvarchar(200)</t>
+  </si>
+  <si>
+    <t>jgugek2</t>
+  </si>
+  <si>
+    <t>nvarchar(40)</t>
+  </si>
+  <si>
+    <t>jdanwy</t>
+  </si>
+  <si>
+    <t>nvarchar(16)</t>
+  </si>
+  <si>
+    <t>jjuk</t>
+  </si>
+  <si>
+    <t>jipgoga</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>jchgoga0</t>
+  </si>
+  <si>
+    <t>jchgoga1</t>
+  </si>
+  <si>
+    <t>jchgoga2</t>
+  </si>
+  <si>
+    <t>jchgoga3</t>
+  </si>
+  <si>
+    <t>jchgoga4</t>
+  </si>
+  <si>
+    <t>jchgoga5</t>
+  </si>
+  <si>
+    <t>jchgoga6</t>
+  </si>
+  <si>
+    <t>jpumcode</t>
+  </si>
+  <si>
+    <t>nvarchar(100)</t>
+  </si>
+  <si>
+    <t>jpumname</t>
+  </si>
+  <si>
+    <t>jdanjung</t>
+  </si>
+  <si>
+    <t>real</t>
+  </si>
+  <si>
+    <t>jgangjung</t>
+  </si>
+  <si>
+    <t>jsagu</t>
+  </si>
+  <si>
+    <t>nvarchar(2)</t>
+  </si>
+  <si>
+    <t>jboxdanwy1</t>
+  </si>
+  <si>
+    <t>jboxsu1</t>
+  </si>
+  <si>
+    <t>jboxdanwy2</t>
+  </si>
+  <si>
+    <t>jboxsu2</t>
+  </si>
+  <si>
+    <t>jilsu</t>
+  </si>
+  <si>
+    <t>jbogan</t>
+  </si>
+  <si>
+    <t>jhayuk</t>
+  </si>
+  <si>
+    <t>jch12</t>
+  </si>
+  <si>
+    <t>jyul12</t>
+  </si>
+  <si>
+    <t>jch13</t>
+  </si>
+  <si>
+    <t>jyul13</t>
+  </si>
+  <si>
+    <t>jch14</t>
+  </si>
+  <si>
+    <t>jyul14</t>
+  </si>
+  <si>
+    <t>jch15</t>
+  </si>
+  <si>
+    <t>jyul15</t>
+  </si>
+  <si>
+    <t>jch16</t>
+  </si>
+  <si>
+    <t>jyul16</t>
+  </si>
+  <si>
+    <t>jch17</t>
+  </si>
+  <si>
+    <t>jyul17</t>
+  </si>
+  <si>
+    <t>jch18</t>
+  </si>
+  <si>
+    <t>jyul18</t>
+  </si>
+  <si>
+    <t>jch19</t>
+  </si>
+  <si>
+    <t>jyul19</t>
+  </si>
+  <si>
+    <t>jbigo</t>
+  </si>
+  <si>
+    <t>nvarchar(60)</t>
+  </si>
+  <si>
+    <t>j_iwol_date</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>j_bigwasei</t>
+  </si>
+  <si>
+    <t>j_link</t>
+  </si>
+  <si>
+    <t>j_misayong</t>
+  </si>
+  <si>
+    <t>j_sang</t>
+  </si>
+  <si>
+    <t>j_sday</t>
+  </si>
+  <si>
+    <t>j_before</t>
+  </si>
+  <si>
+    <t>j_sdate</t>
+  </si>
+  <si>
+    <t>jsayang</t>
+  </si>
+  <si>
+    <t>jchajong</t>
+  </si>
+  <si>
+    <t>w_b_gubn</t>
+  </si>
+  <si>
+    <t>nchar(2)</t>
+  </si>
+  <si>
+    <t>j_ct</t>
+  </si>
+  <si>
+    <t>j_net</t>
+  </si>
+  <si>
+    <t>j_sr</t>
+  </si>
+  <si>
+    <t>j_cavity</t>
+  </si>
+  <si>
+    <t>j_code2</t>
+  </si>
+  <si>
+    <t>j_qc_no</t>
+  </si>
+  <si>
+    <t>jgumnm</t>
+  </si>
+  <si>
+    <t>jgumtype</t>
+  </si>
+  <si>
+    <t>jdoor1</t>
+  </si>
+  <si>
+    <t>jdoor2</t>
+  </si>
+  <si>
+    <t>jthick</t>
+  </si>
+  <si>
+    <t>j_yangsan</t>
+  </si>
+  <si>
+    <t>jolip</t>
+  </si>
+  <si>
+    <t>품목정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>품목대분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>품목중분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>품목명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>규격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금형코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Door1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Door2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유리두께</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스프루</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적입수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KCC바코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포장박스규격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C/T</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1108,1197 +1745,582 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상태(검사완료=5)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등록자코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>적입수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>불량코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>품목코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>픔목코드</t>
+    <t>cif</t>
+  </si>
+  <si>
+    <t>acorp1</t>
+  </si>
+  <si>
+    <t>acorp2</t>
+  </si>
+  <si>
+    <t>acorp3</t>
+  </si>
+  <si>
+    <t>asano1</t>
+  </si>
+  <si>
+    <t>nvarchar(6)</t>
+  </si>
+  <si>
+    <t>asano2</t>
+  </si>
+  <si>
+    <t>asano3</t>
+  </si>
+  <si>
+    <t>nvarchar(10)</t>
+  </si>
+  <si>
+    <t>aname</t>
+  </si>
+  <si>
+    <t>aupte</t>
+  </si>
+  <si>
+    <t>ajong</t>
+  </si>
+  <si>
+    <t>apost1</t>
+  </si>
+  <si>
+    <t>apost2</t>
+  </si>
+  <si>
+    <t>ajuso1</t>
+  </si>
+  <si>
+    <t>nvarchar(120)</t>
+  </si>
+  <si>
+    <t>ajuso2</t>
+  </si>
+  <si>
+    <t>asin</t>
+  </si>
+  <si>
+    <t>abigo</t>
+  </si>
+  <si>
+    <t>nvarchar(MAX)</t>
+  </si>
+  <si>
+    <t>ajegyung</t>
+  </si>
+  <si>
+    <t>afax</t>
+  </si>
+  <si>
+    <t>nvarchar(32)</t>
+  </si>
+  <si>
+    <t>atelno2</t>
+  </si>
+  <si>
+    <t>abuse1</t>
+  </si>
+  <si>
+    <t>adam1</t>
+  </si>
+  <si>
+    <t>nvarchar(24)</t>
+  </si>
+  <si>
+    <t>abuse2</t>
+  </si>
+  <si>
+    <t>adam2</t>
+  </si>
+  <si>
+    <t>abankname1</t>
+  </si>
+  <si>
+    <t>abankyekum1</t>
+  </si>
+  <si>
+    <t>abankke1</t>
+  </si>
+  <si>
+    <t>nvarchar(34)</t>
+  </si>
+  <si>
+    <t>abankname2</t>
+  </si>
+  <si>
+    <t>abankyekum2</t>
+  </si>
+  <si>
+    <t>abankke2</t>
+  </si>
+  <si>
+    <t>agita</t>
+  </si>
+  <si>
+    <t>abonsadam1</t>
+  </si>
+  <si>
+    <t>nvarchar(14)</t>
+  </si>
+  <si>
+    <t>abonsadam2</t>
+  </si>
+  <si>
+    <t>abonsadam3</t>
+  </si>
+  <si>
+    <t>apost1b</t>
+  </si>
+  <si>
+    <t>apost2b</t>
+  </si>
+  <si>
+    <t>ajuso1b</t>
+  </si>
+  <si>
+    <t>ajuso2b</t>
+  </si>
+  <si>
+    <t>aupjong</t>
+  </si>
+  <si>
+    <t>achang</t>
+  </si>
+  <si>
+    <t>afkumek</t>
+  </si>
+  <si>
+    <t>ajukyul</t>
+  </si>
+  <si>
+    <t>avyul</t>
+  </si>
+  <si>
+    <t>aemail</t>
+  </si>
+  <si>
+    <t>adomain</t>
+  </si>
+  <si>
+    <t>ajumi1</t>
+  </si>
+  <si>
+    <t>nvarchar(12)</t>
+  </si>
+  <si>
+    <t>ajumi2</t>
+  </si>
+  <si>
+    <t>ahand</t>
+  </si>
+  <si>
+    <t>atelno</t>
+  </si>
+  <si>
+    <t>aupgubn</t>
+  </si>
+  <si>
+    <t>tinyint</t>
+  </si>
+  <si>
+    <t>avat</t>
+  </si>
+  <si>
+    <t>asekum</t>
+  </si>
+  <si>
+    <t>agani</t>
+  </si>
+  <si>
+    <t>agerae</t>
+  </si>
+  <si>
+    <t>aipkum</t>
+  </si>
+  <si>
+    <t>ajiyuk</t>
+  </si>
+  <si>
+    <t>aibcode</t>
+  </si>
+  <si>
+    <t>asukumil</t>
+  </si>
+  <si>
+    <t>asubigo</t>
+  </si>
+  <si>
+    <t>aasdate</t>
+  </si>
+  <si>
+    <t>aasyear</t>
+  </si>
+  <si>
+    <t>aasmm</t>
+  </si>
+  <si>
+    <t>aascode1</t>
+  </si>
+  <si>
+    <t>aascode2</t>
+  </si>
+  <si>
+    <t>aaskum</t>
+  </si>
+  <si>
+    <t>aasvat</t>
+  </si>
+  <si>
+    <t>awebdate</t>
+  </si>
+  <si>
+    <t>awebyear</t>
+  </si>
+  <si>
+    <t>awebmm</t>
+  </si>
+  <si>
+    <t>awebcode1</t>
+  </si>
+  <si>
+    <t>awebcode2</t>
+  </si>
+  <si>
+    <t>awebkum</t>
+  </si>
+  <si>
+    <t>awebvat</t>
+  </si>
+  <si>
+    <t>adddnum</t>
+  </si>
+  <si>
+    <t>akeyphone</t>
+  </si>
+  <si>
+    <t>amisupogi</t>
+  </si>
+  <si>
+    <t>adanga</t>
+  </si>
+  <si>
+    <t>ahayuk</t>
+  </si>
+  <si>
+    <t>ajukjae</t>
+  </si>
+  <si>
+    <t>amisuhando</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>SSMA_TimeStamp</t>
+  </si>
+  <si>
+    <t>ajungji</t>
+  </si>
+  <si>
+    <t>delflag</t>
+  </si>
+  <si>
+    <t>거래처정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처코드1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처코드2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처코드3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업자번호1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업자번호2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업자번호3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대표자명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우편번호1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우편번호2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팩스번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전화번호2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도메인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>핸드폰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전화번호2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 허용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT </t>
+  </si>
+  <si>
+    <t>대분류코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대분류="00"  상세코드 &lt;&gt; "00"</t>
+  </si>
+  <si>
+    <t>최종상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0=작업전 1=시작 2=진행중 3=작업완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0=작업전 1=시작 2=진행중 3=작업완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0=작업전 1=시작 2=진행중 3=작업완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출고완료=5  미출고=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출고상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D=주간작업  야간작업=N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00010 = 사출  00020=검사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1=작업시작 2=작업중  3=작업종료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사완료=1 미완료=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00010 = 사출  00020=검사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행=1 완료=3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00010 = 사출  00020=검사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>품목분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>J=제품 W=원자재 B=부자재 H=예비부품 G=기타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정코드=001 사원코드=002 가동중단사유=004 불량구분=005 금형구분=006 Door1=102  Door2=103 유형=104 색상=105 유리두께=106 금형보관위치=107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TB_CA510</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>com_cls</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출생산량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출완료량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출불량수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출생산율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출로트번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출공정코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출작업자코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출등록일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출등록자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출투입원자재코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출원자재명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사완료량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사불량수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사누적수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사완료=5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사완료상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사불량코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사출공정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사공정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wdtcd</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TB_FPLAN_WBAD</t>
-  </si>
-  <si>
-    <t>wbqty</t>
-  </si>
-  <si>
-    <t>불량정보</t>
-  </si>
-  <si>
-    <t>로트번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>불량코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등록일자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등록자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TB_FPLAN_WORK</t>
-  </si>
-  <si>
-    <t>varchar(6)</t>
-  </si>
-  <si>
-    <t>wstdt</t>
-  </si>
-  <si>
-    <t>wendt</t>
-  </si>
-  <si>
-    <t>wtable</t>
-  </si>
-  <si>
-    <t>생산작업정보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생산계획번호2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>순번</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업종료일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생산시작시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생산종료시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설비코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생산량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>불량수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생산율</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공정테이블</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업자코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등록일자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생산계획번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TB_FPLAN_WTIME</t>
-  </si>
-  <si>
-    <t>seq</t>
-  </si>
-  <si>
-    <t>wopdv</t>
-  </si>
-  <si>
-    <t>wdtcd</t>
-  </si>
-  <si>
-    <t>wrerm</t>
-  </si>
-  <si>
-    <t>aseq</t>
-  </si>
-  <si>
-    <t>가동비가동정보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>순번</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상세순번</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업시작시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업중지시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비가동코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비가동사유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생산계획번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TB_PC110</t>
-  </si>
-  <si>
-    <t>machcd</t>
-  </si>
-  <si>
-    <t>machno</t>
-  </si>
-  <si>
-    <t>machname</t>
-  </si>
-  <si>
-    <t>machdate</t>
-  </si>
-  <si>
-    <t>machstdate</t>
-  </si>
-  <si>
-    <t>macheddate</t>
-  </si>
-  <si>
-    <t>machshot</t>
-  </si>
-  <si>
-    <t>machgugek03</t>
-  </si>
-  <si>
-    <t>machgugek02</t>
-  </si>
-  <si>
-    <t>machgugek01</t>
-  </si>
-  <si>
-    <t>machcavity</t>
-  </si>
-  <si>
-    <t>machuse</t>
-  </si>
-  <si>
-    <t>machcha</t>
-  </si>
-  <si>
-    <t>machjaejak</t>
-  </si>
-  <si>
-    <t>machcltcd</t>
-  </si>
-  <si>
-    <t>machcltnm</t>
-  </si>
-  <si>
-    <t>machplace</t>
-  </si>
-  <si>
-    <t>machamt</t>
-  </si>
-  <si>
-    <t>machwon</t>
-  </si>
-  <si>
-    <t>machgrade</t>
-  </si>
-  <si>
-    <t>machgram</t>
-  </si>
-  <si>
-    <t>machncha</t>
-  </si>
-  <si>
-    <t>machnum</t>
-  </si>
-  <si>
-    <t>inpcode</t>
-  </si>
-  <si>
-    <t>injpum</t>
-  </si>
-  <si>
-    <t>machgumnm</t>
-  </si>
-  <si>
-    <t>금형정보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>품번</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금형번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최초입고일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제작시작일자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제작종료일자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수명예상SHOT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금형규격03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금형규격02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAVITY수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용기계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>차종(모델명)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금형제작업체</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래선</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금형보관위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>원재료명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>담당자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금형등급</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제품중량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N차금형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등록일자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등록자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>품명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금형명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jcode</t>
-  </si>
-  <si>
-    <t>jkey</t>
-  </si>
-  <si>
-    <t>nvarchar(20)</t>
-  </si>
-  <si>
-    <t>j_dae</t>
-  </si>
-  <si>
-    <t>nvarchar(4)</t>
-  </si>
-  <si>
-    <t>j_jung</t>
-  </si>
-  <si>
-    <t>nvarchar(8)</t>
-  </si>
-  <si>
-    <t>jpum</t>
-  </si>
-  <si>
-    <t>nvarchar(80)</t>
-  </si>
-  <si>
-    <t>jgugek</t>
-  </si>
-  <si>
-    <t>nvarchar(200)</t>
-  </si>
-  <si>
-    <t>jgugek2</t>
-  </si>
-  <si>
-    <t>nvarchar(40)</t>
-  </si>
-  <si>
-    <t>jdanwy</t>
-  </si>
-  <si>
-    <t>nvarchar(16)</t>
-  </si>
-  <si>
-    <t>jjuk</t>
-  </si>
-  <si>
-    <t>jipgoga</t>
-  </si>
-  <si>
-    <t>money</t>
-  </si>
-  <si>
-    <t>jchgoga0</t>
-  </si>
-  <si>
-    <t>jchgoga1</t>
-  </si>
-  <si>
-    <t>jchgoga2</t>
-  </si>
-  <si>
-    <t>jchgoga3</t>
-  </si>
-  <si>
-    <t>jchgoga4</t>
-  </si>
-  <si>
-    <t>jchgoga5</t>
-  </si>
-  <si>
-    <t>jchgoga6</t>
-  </si>
-  <si>
-    <t>jpumcode</t>
-  </si>
-  <si>
-    <t>nvarchar(100)</t>
-  </si>
-  <si>
-    <t>jpumname</t>
-  </si>
-  <si>
-    <t>jdanjung</t>
-  </si>
-  <si>
-    <t>real</t>
-  </si>
-  <si>
-    <t>jgangjung</t>
-  </si>
-  <si>
-    <t>jsagu</t>
-  </si>
-  <si>
-    <t>nvarchar(2)</t>
-  </si>
-  <si>
-    <t>jboxdanwy1</t>
-  </si>
-  <si>
-    <t>jboxsu1</t>
-  </si>
-  <si>
-    <t>jboxdanwy2</t>
-  </si>
-  <si>
-    <t>jboxsu2</t>
-  </si>
-  <si>
-    <t>jilsu</t>
-  </si>
-  <si>
-    <t>jbogan</t>
-  </si>
-  <si>
-    <t>jhayuk</t>
-  </si>
-  <si>
-    <t>jch12</t>
-  </si>
-  <si>
-    <t>jyul12</t>
-  </si>
-  <si>
-    <t>jch13</t>
-  </si>
-  <si>
-    <t>jyul13</t>
-  </si>
-  <si>
-    <t>jch14</t>
-  </si>
-  <si>
-    <t>jyul14</t>
-  </si>
-  <si>
-    <t>jch15</t>
-  </si>
-  <si>
-    <t>jyul15</t>
-  </si>
-  <si>
-    <t>jch16</t>
-  </si>
-  <si>
-    <t>jyul16</t>
-  </si>
-  <si>
-    <t>jch17</t>
-  </si>
-  <si>
-    <t>jyul17</t>
-  </si>
-  <si>
-    <t>jch18</t>
-  </si>
-  <si>
-    <t>jyul18</t>
-  </si>
-  <si>
-    <t>jch19</t>
-  </si>
-  <si>
-    <t>jyul19</t>
-  </si>
-  <si>
-    <t>jbigo</t>
-  </si>
-  <si>
-    <t>nvarchar(60)</t>
-  </si>
-  <si>
-    <t>j_iwol_date</t>
-  </si>
-  <si>
-    <t>datetime</t>
-  </si>
-  <si>
-    <t>j_bigwasei</t>
-  </si>
-  <si>
-    <t>j_link</t>
-  </si>
-  <si>
-    <t>j_misayong</t>
-  </si>
-  <si>
-    <t>j_sang</t>
-  </si>
-  <si>
-    <t>j_sday</t>
-  </si>
-  <si>
-    <t>j_before</t>
-  </si>
-  <si>
-    <t>j_sdate</t>
-  </si>
-  <si>
-    <t>jsayang</t>
-  </si>
-  <si>
-    <t>jchajong</t>
-  </si>
-  <si>
-    <t>w_b_gubn</t>
-  </si>
-  <si>
-    <t>nchar(2)</t>
-  </si>
-  <si>
-    <t>j_ct</t>
-  </si>
-  <si>
-    <t>j_net</t>
-  </si>
-  <si>
-    <t>j_sr</t>
-  </si>
-  <si>
-    <t>j_cavity</t>
-  </si>
-  <si>
-    <t>j_code2</t>
-  </si>
-  <si>
-    <t>j_qc_no</t>
-  </si>
-  <si>
-    <t>jgumnm</t>
-  </si>
-  <si>
-    <t>jgumtype</t>
-  </si>
-  <si>
-    <t>jdoor1</t>
-  </si>
-  <si>
-    <t>jdoor2</t>
-  </si>
-  <si>
-    <t>jthick</t>
-  </si>
-  <si>
-    <t>j_yangsan</t>
-  </si>
-  <si>
-    <t>jolip</t>
-  </si>
-  <si>
-    <t>품목정보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>품목대분류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>품목중분류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>품목명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>규격</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>단위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금형코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>색상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Door1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Door2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>양산</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유리두께</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스프루</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>적입수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KCC바코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포장박스규격</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C/T</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cif</t>
-  </si>
-  <si>
-    <t>acorp1</t>
-  </si>
-  <si>
-    <t>acorp2</t>
-  </si>
-  <si>
-    <t>acorp3</t>
-  </si>
-  <si>
-    <t>asano1</t>
-  </si>
-  <si>
-    <t>nvarchar(6)</t>
-  </si>
-  <si>
-    <t>asano2</t>
-  </si>
-  <si>
-    <t>asano3</t>
-  </si>
-  <si>
-    <t>nvarchar(10)</t>
-  </si>
-  <si>
-    <t>aname</t>
-  </si>
-  <si>
-    <t>aupte</t>
-  </si>
-  <si>
-    <t>ajong</t>
-  </si>
-  <si>
-    <t>apost1</t>
-  </si>
-  <si>
-    <t>apost2</t>
-  </si>
-  <si>
-    <t>ajuso1</t>
-  </si>
-  <si>
-    <t>nvarchar(120)</t>
-  </si>
-  <si>
-    <t>ajuso2</t>
-  </si>
-  <si>
-    <t>asin</t>
-  </si>
-  <si>
-    <t>abigo</t>
-  </si>
-  <si>
-    <t>nvarchar(MAX)</t>
-  </si>
-  <si>
-    <t>ajegyung</t>
-  </si>
-  <si>
-    <t>afax</t>
-  </si>
-  <si>
-    <t>nvarchar(32)</t>
-  </si>
-  <si>
-    <t>atelno2</t>
-  </si>
-  <si>
-    <t>abuse1</t>
-  </si>
-  <si>
-    <t>adam1</t>
-  </si>
-  <si>
-    <t>nvarchar(24)</t>
-  </si>
-  <si>
-    <t>abuse2</t>
-  </si>
-  <si>
-    <t>adam2</t>
-  </si>
-  <si>
-    <t>abankname1</t>
-  </si>
-  <si>
-    <t>abankyekum1</t>
-  </si>
-  <si>
-    <t>abankke1</t>
-  </si>
-  <si>
-    <t>nvarchar(34)</t>
-  </si>
-  <si>
-    <t>abankname2</t>
-  </si>
-  <si>
-    <t>abankyekum2</t>
-  </si>
-  <si>
-    <t>abankke2</t>
-  </si>
-  <si>
-    <t>agita</t>
-  </si>
-  <si>
-    <t>abonsadam1</t>
-  </si>
-  <si>
-    <t>nvarchar(14)</t>
-  </si>
-  <si>
-    <t>abonsadam2</t>
-  </si>
-  <si>
-    <t>abonsadam3</t>
-  </si>
-  <si>
-    <t>apost1b</t>
-  </si>
-  <si>
-    <t>apost2b</t>
-  </si>
-  <si>
-    <t>ajuso1b</t>
-  </si>
-  <si>
-    <t>ajuso2b</t>
-  </si>
-  <si>
-    <t>aupjong</t>
-  </si>
-  <si>
-    <t>achang</t>
-  </si>
-  <si>
-    <t>afkumek</t>
-  </si>
-  <si>
-    <t>ajukyul</t>
-  </si>
-  <si>
-    <t>avyul</t>
-  </si>
-  <si>
-    <t>aemail</t>
-  </si>
-  <si>
-    <t>adomain</t>
-  </si>
-  <si>
-    <t>ajumi1</t>
-  </si>
-  <si>
-    <t>nvarchar(12)</t>
-  </si>
-  <si>
-    <t>ajumi2</t>
-  </si>
-  <si>
-    <t>ahand</t>
-  </si>
-  <si>
-    <t>atelno</t>
-  </si>
-  <si>
-    <t>aupgubn</t>
-  </si>
-  <si>
-    <t>tinyint</t>
-  </si>
-  <si>
-    <t>avat</t>
-  </si>
-  <si>
-    <t>asekum</t>
-  </si>
-  <si>
-    <t>agani</t>
-  </si>
-  <si>
-    <t>agerae</t>
-  </si>
-  <si>
-    <t>aipkum</t>
-  </si>
-  <si>
-    <t>ajiyuk</t>
-  </si>
-  <si>
-    <t>aibcode</t>
-  </si>
-  <si>
-    <t>asukumil</t>
-  </si>
-  <si>
-    <t>asubigo</t>
-  </si>
-  <si>
-    <t>aasdate</t>
-  </si>
-  <si>
-    <t>aasyear</t>
-  </si>
-  <si>
-    <t>aasmm</t>
-  </si>
-  <si>
-    <t>aascode1</t>
-  </si>
-  <si>
-    <t>aascode2</t>
-  </si>
-  <si>
-    <t>aaskum</t>
-  </si>
-  <si>
-    <t>aasvat</t>
-  </si>
-  <si>
-    <t>awebdate</t>
-  </si>
-  <si>
-    <t>awebyear</t>
-  </si>
-  <si>
-    <t>awebmm</t>
-  </si>
-  <si>
-    <t>awebcode1</t>
-  </si>
-  <si>
-    <t>awebcode2</t>
-  </si>
-  <si>
-    <t>awebkum</t>
-  </si>
-  <si>
-    <t>awebvat</t>
-  </si>
-  <si>
-    <t>adddnum</t>
-  </si>
-  <si>
-    <t>akeyphone</t>
-  </si>
-  <si>
-    <t>amisupogi</t>
-  </si>
-  <si>
-    <t>adanga</t>
-  </si>
-  <si>
-    <t>ahayuk</t>
-  </si>
-  <si>
-    <t>ajukjae</t>
-  </si>
-  <si>
-    <t>amisuhando</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>SSMA_TimeStamp</t>
-  </si>
-  <si>
-    <t>ajungji</t>
-  </si>
-  <si>
-    <t>delflag</t>
-  </si>
-  <si>
-    <t>거래처정보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래처코드1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래처코드2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래처코드3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래처명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사업자번호1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사업자번호2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사업자번호3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대표자명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>업태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>종목</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>우편번호1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>우편번호2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상세주소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>팩스번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전화번호2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>담당자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이메일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>도메인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>핸드폰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전화번호2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 허용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT </t>
-  </si>
-  <si>
-    <t>대분류코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대분류="00"  상세코드 &lt;&gt; "00"</t>
-  </si>
-  <si>
-    <t>최종상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0=작업전 1=시작 2=진행중 3=작업완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사출상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0=작업전 1=시작 2=진행중 3=작업완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0=작업전 1=시작 2=진행중 3=작업완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출고완료=5  미출고=0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출고상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업구분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D=주간작업  야간작업=N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공정코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>00010 = 사출  00020=검사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1=작업시작 2=작업중  3=작업종료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공정코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사완료=1 미완료=0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공정코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>00010 = 사출  00020=검사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공정코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행=1 완료=3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>00010 = 사출  00020=검사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>품목분류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>J=제품 W=원자재 B=부자재 H=예비부품 G=기타</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공정코드=001 사원코드=002 가동중단사유=004 불량구분=005 금형구분=006 Door1=102  Door2=103 유형=104 색상=105 유리두께=106 금형보관위치=107</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TB_CA510</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>com_cls</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2621,7 +2643,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I501"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2659,7 +2681,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>654</v>
+        <v>639</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -2670,13 +2692,13 @@
         <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -2685,10 +2707,10 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
       <c r="I2" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -2699,7 +2721,7 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>656</v>
+        <v>641</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -2711,10 +2733,10 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
       <c r="I3" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -2822,7 +2844,7 @@
         <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -2845,7 +2867,7 @@
         <v>8</v>
       </c>
       <c r="H10" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -2868,7 +2890,7 @@
         <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -2891,7 +2913,7 @@
         <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -2914,7 +2936,7 @@
         <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -2934,7 +2956,7 @@
         <v>53</v>
       </c>
       <c r="H14" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -2962,7 +2984,7 @@
         <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="D16" t="s">
         <v>55</v>
@@ -3325,7 +3347,7 @@
         <v>8</v>
       </c>
       <c r="H37" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -3348,7 +3370,7 @@
         <v>8</v>
       </c>
       <c r="H38" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -3371,7 +3393,7 @@
         <v>8</v>
       </c>
       <c r="H39" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -3394,7 +3416,7 @@
         <v>8</v>
       </c>
       <c r="H40" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -4111,7 +4133,7 @@
         <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
@@ -4134,7 +4156,7 @@
         <v>8</v>
       </c>
       <c r="H89" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -4157,7 +4179,7 @@
         <v>8</v>
       </c>
       <c r="H90" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
@@ -4180,7 +4202,7 @@
         <v>8</v>
       </c>
       <c r="H91" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
@@ -4203,7 +4225,7 @@
         <v>8</v>
       </c>
       <c r="H92" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
@@ -4827,7 +4849,7 @@
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
@@ -4850,7 +4872,7 @@
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
@@ -4873,7 +4895,7 @@
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
@@ -5301,7 +5323,7 @@
         <v>186</v>
       </c>
       <c r="C164" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="D164" t="s">
         <v>206</v>
@@ -5310,7 +5332,7 @@
         <v>78</v>
       </c>
       <c r="I164" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
@@ -5321,7 +5343,7 @@
         <v>186</v>
       </c>
       <c r="C165" t="s">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="D165" t="s">
         <v>207</v>
@@ -5330,7 +5352,7 @@
         <v>78</v>
       </c>
       <c r="I165" t="s">
-        <v>661</v>
+        <v>646</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
@@ -5341,7 +5363,7 @@
         <v>186</v>
       </c>
       <c r="C166" t="s">
-        <v>662</v>
+        <v>647</v>
       </c>
       <c r="D166" t="s">
         <v>208</v>
@@ -5350,7 +5372,7 @@
         <v>78</v>
       </c>
       <c r="I166" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -5361,7 +5383,7 @@
         <v>186</v>
       </c>
       <c r="C167" t="s">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="D167" t="s">
         <v>209</v>
@@ -5370,7 +5392,7 @@
         <v>78</v>
       </c>
       <c r="I167" t="s">
-        <v>664</v>
+        <v>649</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
@@ -5513,7 +5535,7 @@
         <v>186</v>
       </c>
       <c r="C177" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="D177" t="s">
         <v>217</v>
@@ -5522,7 +5544,7 @@
         <v>78</v>
       </c>
       <c r="I177" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
@@ -5578,7 +5600,7 @@
         <v>186</v>
       </c>
       <c r="C181" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="D181" t="s">
         <v>219</v>
@@ -5587,7 +5609,7 @@
         <v>39</v>
       </c>
       <c r="I181" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
@@ -5876,7 +5898,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B201" t="s">
         <v>259</v>
@@ -5894,12 +5916,12 @@
         <v>8</v>
       </c>
       <c r="H201" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B202" t="s">
         <v>259</v>
@@ -5917,18 +5939,18 @@
         <v>8</v>
       </c>
       <c r="H202" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B203" t="s">
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D203" t="s">
         <v>187</v>
@@ -5940,18 +5962,18 @@
         <v>8</v>
       </c>
       <c r="H203" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B204" t="s">
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>185</v>
+        <v>673</v>
       </c>
       <c r="D204" t="s">
         <v>62</v>
@@ -5963,18 +5985,18 @@
         <v>8</v>
       </c>
       <c r="H204" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B205" t="s">
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>252</v>
+        <v>674</v>
       </c>
       <c r="D205" t="s">
         <v>219</v>
@@ -5983,18 +6005,18 @@
         <v>39</v>
       </c>
       <c r="I205" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B206" t="s">
         <v>259</v>
       </c>
       <c r="C206" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D206" t="s">
         <v>260</v>
@@ -6005,13 +6027,13 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B207" t="s">
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D207" t="s">
         <v>262</v>
@@ -6022,7 +6044,7 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B208" t="s">
         <v>259</v>
@@ -6039,13 +6061,13 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B209" t="s">
         <v>259</v>
       </c>
       <c r="C209" t="s">
-        <v>299</v>
+        <v>669</v>
       </c>
       <c r="D209" t="s">
         <v>263</v>
@@ -6056,13 +6078,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B210" t="s">
         <v>259</v>
       </c>
       <c r="C210" t="s">
-        <v>300</v>
+        <v>670</v>
       </c>
       <c r="D210" t="s">
         <v>264</v>
@@ -6073,7 +6095,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B211" t="s">
         <v>259</v>
@@ -6087,13 +6109,13 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B212" t="s">
         <v>259</v>
       </c>
       <c r="C212" t="s">
-        <v>301</v>
+        <v>671</v>
       </c>
       <c r="D212" t="s">
         <v>266</v>
@@ -6104,7 +6126,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B213" t="s">
         <v>259</v>
@@ -6118,13 +6140,13 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B214" t="s">
         <v>259</v>
       </c>
       <c r="C214" t="s">
-        <v>302</v>
+        <v>672</v>
       </c>
       <c r="D214" t="s">
         <v>269</v>
@@ -6135,13 +6157,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B215" t="s">
         <v>259</v>
       </c>
       <c r="C215" t="s">
-        <v>303</v>
+        <v>675</v>
       </c>
       <c r="D215" t="s">
         <v>271</v>
@@ -6152,7 +6174,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B216" t="s">
         <v>259</v>
@@ -6166,7 +6188,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B217" t="s">
         <v>259</v>
@@ -6180,7 +6202,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B218" t="s">
         <v>259</v>
@@ -6194,13 +6216,13 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B219" t="s">
         <v>259</v>
       </c>
       <c r="C219" t="s">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="D219" t="s">
         <v>206</v>
@@ -6209,18 +6231,18 @@
         <v>78</v>
       </c>
       <c r="I219" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B220" t="s">
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>304</v>
+        <v>676</v>
       </c>
       <c r="D220" t="s">
         <v>27</v>
@@ -6231,13 +6253,13 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B221" t="s">
         <v>259</v>
       </c>
       <c r="C221" t="s">
-        <v>305</v>
+        <v>677</v>
       </c>
       <c r="D221" t="s">
         <v>83</v>
@@ -6248,13 +6270,13 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B222" t="s">
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>306</v>
+        <v>678</v>
       </c>
       <c r="D222" t="s">
         <v>275</v>
@@ -6265,13 +6287,13 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B223" t="s">
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>315</v>
+        <v>679</v>
       </c>
       <c r="D223" t="s">
         <v>276</v>
@@ -6282,13 +6304,13 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B224" t="s">
         <v>259</v>
       </c>
       <c r="C224" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D224" t="s">
         <v>277</v>
@@ -6299,13 +6321,13 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B225" t="s">
         <v>259</v>
       </c>
       <c r="C225" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D225" t="s">
         <v>278</v>
@@ -6316,13 +6338,13 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B226" t="s">
         <v>259</v>
       </c>
       <c r="C226" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D226" t="s">
         <v>279</v>
@@ -6333,13 +6355,13 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B227" t="s">
         <v>259</v>
       </c>
       <c r="C227" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D227" t="s">
         <v>280</v>
@@ -6350,13 +6372,13 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B228" t="s">
         <v>259</v>
       </c>
       <c r="C228" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D228" t="s">
         <v>281</v>
@@ -6367,13 +6389,13 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B229" t="s">
         <v>259</v>
       </c>
       <c r="C229" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D229" t="s">
         <v>282</v>
@@ -6384,13 +6406,13 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B230" t="s">
         <v>259</v>
       </c>
       <c r="C230" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D230" t="s">
         <v>283</v>
@@ -6401,13 +6423,13 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B231" t="s">
         <v>259</v>
       </c>
       <c r="C231" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D231" t="s">
         <v>284</v>
@@ -6418,7 +6440,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B232" t="s">
         <v>259</v>
@@ -6432,7 +6454,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B233" t="s">
         <v>259</v>
@@ -6446,7 +6468,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B234" t="s">
         <v>259</v>
@@ -6460,7 +6482,7 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B235" t="s">
         <v>259</v>
@@ -6474,7 +6496,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B236" t="s">
         <v>259</v>
@@ -6488,7 +6510,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B237" t="s">
         <v>259</v>
@@ -6502,7 +6524,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B238" t="s">
         <v>259</v>
@@ -6516,7 +6538,7 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B239" t="s">
         <v>259</v>
@@ -6530,7 +6552,7 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B240" t="s">
         <v>259</v>
@@ -6544,13 +6566,13 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B241" t="s">
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D241" t="s">
         <v>293</v>
@@ -6561,13 +6583,13 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="B242" t="s">
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D242" t="s">
         <v>294</v>
@@ -6578,10 +6600,10 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B243" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C243" t="s">
         <v>93</v>
@@ -6596,15 +6618,15 @@
         <v>8</v>
       </c>
       <c r="H243" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B244" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C244" t="s">
         <v>94</v>
@@ -6619,18 +6641,18 @@
         <v>8</v>
       </c>
       <c r="H244" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B245" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C245" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D245" t="s">
         <v>62</v>
@@ -6642,18 +6664,18 @@
         <v>8</v>
       </c>
       <c r="H245" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B246" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C246" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D246" t="s">
         <v>187</v>
@@ -6665,15 +6687,15 @@
         <v>8</v>
       </c>
       <c r="H246" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B247" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C247" t="s">
         <v>176</v>
@@ -6688,18 +6710,18 @@
         <v>8</v>
       </c>
       <c r="H247" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B248" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C248" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="D248" t="s">
         <v>219</v>
@@ -6708,18 +6730,18 @@
         <v>39</v>
       </c>
       <c r="I248" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B249" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C249" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D249" t="s">
         <v>260</v>
@@ -6730,13 +6752,13 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B250" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C250" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D250" t="s">
         <v>262</v>
@@ -6747,13 +6769,13 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B251" t="s">
+        <v>310</v>
+      </c>
+      <c r="C251" t="s">
         <v>318</v>
-      </c>
-      <c r="C251" t="s">
-        <v>327</v>
       </c>
       <c r="D251" t="s">
         <v>232</v>
@@ -6764,13 +6786,13 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B252" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C252" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D252" t="s">
         <v>263</v>
@@ -6781,13 +6803,13 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B253" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C253" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D253" t="s">
         <v>264</v>
@@ -6798,13 +6820,13 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B254" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C254" t="s">
-        <v>329</v>
+        <v>680</v>
       </c>
       <c r="D254" t="s">
         <v>265</v>
@@ -6815,13 +6837,13 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B255" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C255" t="s">
-        <v>301</v>
+        <v>681</v>
       </c>
       <c r="D255" t="s">
         <v>266</v>
@@ -6832,16 +6854,16 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B256" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C256" t="s">
-        <v>331</v>
+        <v>682</v>
       </c>
       <c r="D256" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E256" t="s">
         <v>69</v>
@@ -6849,10 +6871,10 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B257" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D257" t="s">
         <v>267</v>
@@ -6863,10 +6885,10 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B258" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D258" t="s">
         <v>269</v>
@@ -6877,13 +6899,13 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B259" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C259" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="D259" t="s">
         <v>271</v>
@@ -6894,13 +6916,13 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
+        <v>687</v>
+      </c>
+      <c r="B260" t="s">
+        <v>310</v>
+      </c>
+      <c r="C260" t="s">
         <v>322</v>
-      </c>
-      <c r="B260" t="s">
-        <v>318</v>
-      </c>
-      <c r="C260" t="s">
-        <v>333</v>
       </c>
       <c r="D260" t="s">
         <v>272</v>
@@ -6911,10 +6933,10 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B261" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D261" t="s">
         <v>273</v>
@@ -6925,10 +6947,10 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B262" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D262" t="s">
         <v>274</v>
@@ -6939,13 +6961,13 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B263" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C263" t="s">
-        <v>334</v>
+        <v>647</v>
       </c>
       <c r="D263" t="s">
         <v>206</v>
@@ -6953,16 +6975,19 @@
       <c r="E263" t="s">
         <v>78</v>
       </c>
+      <c r="I263" t="s">
+        <v>683</v>
+      </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B264" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C264" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D264" t="s">
         <v>27</v>
@@ -6973,10 +6998,10 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B265" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D265" t="s">
         <v>83</v>
@@ -6987,10 +7012,10 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B266" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D266" t="s">
         <v>114</v>
@@ -7001,10 +7026,10 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B267" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D267" t="s">
         <v>115</v>
@@ -7015,10 +7040,10 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B268" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D268" t="s">
         <v>160</v>
@@ -7029,16 +7054,16 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B269" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C269" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D269" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E269" t="s">
         <v>69</v>
@@ -7046,13 +7071,13 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B270" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C270" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="D270" t="s">
         <v>146</v>
@@ -7061,21 +7086,21 @@
         <v>18</v>
       </c>
       <c r="I270" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B271" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C271" t="s">
-        <v>337</v>
+        <v>685</v>
       </c>
       <c r="D271" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E271" t="s">
         <v>39</v>
@@ -7083,13 +7108,13 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>322</v>
+        <v>687</v>
       </c>
       <c r="B272" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C272" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="D272" t="s">
         <v>55</v>
@@ -7100,10 +7125,10 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B273" t="s">
-        <v>340</v>
+        <v>689</v>
       </c>
       <c r="C273" t="s">
         <v>93</v>
@@ -7118,15 +7143,15 @@
         <v>8</v>
       </c>
       <c r="H273" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B274" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C274" t="s">
         <v>94</v>
@@ -7141,18 +7166,18 @@
         <v>8</v>
       </c>
       <c r="H274" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B275" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C275" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="D275" t="s">
         <v>62</v>
@@ -7164,15 +7189,15 @@
         <v>8</v>
       </c>
       <c r="H275" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B276" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C276" t="s">
         <v>176</v>
@@ -7187,18 +7212,18 @@
         <v>8</v>
       </c>
       <c r="H276" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B277" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C277" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="D277" t="s">
         <v>219</v>
@@ -7210,24 +7235,24 @@
         <v>8</v>
       </c>
       <c r="H277" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
       <c r="I277" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B278" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C278" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="D278" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E278" t="s">
         <v>39</v>
@@ -7236,21 +7261,21 @@
         <v>8</v>
       </c>
       <c r="H278" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B279" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C279" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D279" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="E279" t="s">
         <v>65</v>
@@ -7258,13 +7283,13 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B280" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C280" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="D280" t="s">
         <v>27</v>
@@ -7275,13 +7300,13 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B281" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C281" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D281" t="s">
         <v>83</v>
@@ -7292,13 +7317,13 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B282" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C282" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D282" t="s">
         <v>187</v>
@@ -7309,10 +7334,10 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B283" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C283" t="s">
         <v>93</v>
@@ -7327,15 +7352,15 @@
         <v>8</v>
       </c>
       <c r="H283" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B284" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C284" t="s">
         <v>94</v>
@@ -7350,15 +7375,15 @@
         <v>8</v>
       </c>
       <c r="H284" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B285" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C285" t="s">
         <v>239</v>
@@ -7373,18 +7398,18 @@
         <v>8</v>
       </c>
       <c r="H285" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B286" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C286" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D286" t="s">
         <v>189</v>
@@ -7396,18 +7421,18 @@
         <v>8</v>
       </c>
       <c r="H286" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B287" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C287" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="D287" t="s">
         <v>220</v>
@@ -7419,41 +7444,41 @@
         <v>8</v>
       </c>
       <c r="H287" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B288" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C288" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="D288" t="s">
         <v>219</v>
       </c>
       <c r="E288" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="I288" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B289" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C289" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D289" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="E289" t="s">
         <v>48</v>
@@ -7461,16 +7486,16 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B290" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C290" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="D290" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="E290" t="s">
         <v>48</v>
@@ -7478,13 +7503,13 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B291" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C291" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="D291" t="s">
         <v>260</v>
@@ -7495,13 +7520,13 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B292" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C292" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D292" t="s">
         <v>262</v>
@@ -7512,13 +7537,13 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B293" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C293" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="D293" t="s">
         <v>232</v>
@@ -7529,13 +7554,13 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B294" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C294" t="s">
-        <v>359</v>
+        <v>298</v>
       </c>
       <c r="D294" t="s">
         <v>263</v>
@@ -7546,13 +7571,13 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B295" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C295" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="D295" t="s">
         <v>264</v>
@@ -7563,10 +7588,10 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B296" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D296" t="s">
         <v>265</v>
@@ -7577,13 +7602,13 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B297" t="s">
+        <v>334</v>
+      </c>
+      <c r="C297" t="s">
         <v>347</v>
-      </c>
-      <c r="C297" t="s">
-        <v>361</v>
       </c>
       <c r="D297" t="s">
         <v>266</v>
@@ -7594,10 +7619,10 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B298" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D298" t="s">
         <v>267</v>
@@ -7608,13 +7633,13 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B299" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C299" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="D299" t="s">
         <v>269</v>
@@ -7625,16 +7650,16 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B300" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C300" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="D300" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="E300" t="s">
         <v>12</v>
@@ -7642,13 +7667,13 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B301" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C301" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="D301" t="s">
         <v>271</v>
@@ -7659,13 +7684,13 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B302" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C302" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="D302" t="s">
         <v>272</v>
@@ -7676,13 +7701,13 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B303" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C303" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="D303" t="s">
         <v>206</v>
@@ -7691,18 +7716,18 @@
         <v>78</v>
       </c>
       <c r="I303" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
+        <v>339</v>
+      </c>
+      <c r="B304" t="s">
+        <v>334</v>
+      </c>
+      <c r="C304" t="s">
         <v>352</v>
-      </c>
-      <c r="B304" t="s">
-        <v>347</v>
-      </c>
-      <c r="C304" t="s">
-        <v>366</v>
       </c>
       <c r="D304" t="s">
         <v>27</v>
@@ -7713,13 +7738,13 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B305" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C305" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D305" t="s">
         <v>83</v>
@@ -7730,13 +7755,13 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B306" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C306" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="D306" t="s">
         <v>187</v>
@@ -7747,10 +7772,10 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B307" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C307" t="s">
         <v>93</v>
@@ -7765,15 +7790,15 @@
         <v>8</v>
       </c>
       <c r="H307" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B308" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C308" t="s">
         <v>94</v>
@@ -7788,15 +7813,15 @@
         <v>8</v>
       </c>
       <c r="H308" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B309" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C309" t="s">
         <v>239</v>
@@ -7811,18 +7836,18 @@
         <v>8</v>
       </c>
       <c r="H309" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B310" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C310" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D310" t="s">
         <v>220</v>
@@ -7834,21 +7859,21 @@
         <v>8</v>
       </c>
       <c r="H310" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B311" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C311" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="D311" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="E311" t="s">
         <v>31</v>
@@ -7857,15 +7882,15 @@
         <v>8</v>
       </c>
       <c r="H311" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B312" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C312" t="s">
         <v>252</v>
@@ -7874,21 +7899,21 @@
         <v>219</v>
       </c>
       <c r="E312" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="I312" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B313" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C313" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="D313" t="s">
         <v>260</v>
@@ -7899,13 +7924,13 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B314" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C314" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D314" t="s">
         <v>262</v>
@@ -7916,13 +7941,13 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B315" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="D315" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="E315" t="s">
         <v>78</v>
@@ -7930,16 +7955,16 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B316" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C316" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D316" t="s">
-        <v>371</v>
+        <v>688</v>
       </c>
       <c r="E316" t="s">
         <v>39</v>
@@ -7947,16 +7972,16 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B317" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C317" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D317" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="E317" t="s">
         <v>13</v>
@@ -7964,13 +7989,13 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B318" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="D318" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="E318" t="s">
         <v>31</v>
@@ -7978,13 +8003,13 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B319" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C319" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="D319" t="s">
         <v>187</v>
@@ -7996,21 +8021,21 @@
         <v>8</v>
       </c>
       <c r="H319" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B320" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C320" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="D320" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="E320" t="s">
         <v>10</v>
@@ -8019,21 +8044,21 @@
         <v>8</v>
       </c>
       <c r="H320" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B321" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C321" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="D321" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="E321" t="s">
         <v>10</v>
@@ -8041,16 +8066,16 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B322" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C322" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="D322" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="E322" t="s">
         <v>10</v>
@@ -8058,16 +8083,16 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B323" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C323" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="D323" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="E323" t="s">
         <v>48</v>
@@ -8075,16 +8100,16 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B324" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C324" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="D324" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="E324" t="s">
         <v>48</v>
@@ -8092,16 +8117,16 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B325" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C325" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="D325" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="E325" t="s">
         <v>48</v>
@@ -8109,16 +8134,16 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B326" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C326" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="D326" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="E326" t="s">
         <v>37</v>
@@ -8126,16 +8151,16 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B327" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C327" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="D327" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="E327" t="s">
         <v>37</v>
@@ -8143,16 +8168,16 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B328" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C328" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="D328" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="E328" t="s">
         <v>37</v>
@@ -8160,16 +8185,16 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B329" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C329" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="D329" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="E329" t="s">
         <v>37</v>
@@ -8177,16 +8202,16 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B330" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C330" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="D330" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="E330" t="s">
         <v>10</v>
@@ -8194,16 +8219,16 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B331" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C331" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="D331" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="E331" t="s">
         <v>10</v>
@@ -8211,16 +8236,16 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B332" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C332" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D332" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="E332" t="s">
         <v>10</v>
@@ -8228,13 +8253,13 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B333" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D333" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="E333" t="s">
         <v>10</v>
@@ -8242,16 +8267,16 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B334" t="s">
+        <v>367</v>
+      </c>
+      <c r="C334" t="s">
+        <v>407</v>
+      </c>
+      <c r="D334" t="s">
         <v>382</v>
-      </c>
-      <c r="C334" t="s">
-        <v>422</v>
-      </c>
-      <c r="D334" t="s">
-        <v>397</v>
       </c>
       <c r="E334" t="s">
         <v>10</v>
@@ -8259,16 +8284,16 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B335" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C335" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D335" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="E335" t="s">
         <v>10</v>
@@ -8276,13 +8301,13 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B336" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D336" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="E336" t="s">
         <v>10</v>
@@ -8290,13 +8315,13 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B337" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D337" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="E337" t="s">
         <v>69</v>
@@ -8304,16 +8329,16 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
+        <v>394</v>
+      </c>
+      <c r="B338" t="s">
+        <v>367</v>
+      </c>
+      <c r="C338" t="s">
         <v>409</v>
       </c>
-      <c r="B338" t="s">
-        <v>382</v>
-      </c>
-      <c r="C338" t="s">
-        <v>424</v>
-      </c>
       <c r="D338" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="E338" t="s">
         <v>10</v>
@@ -8321,13 +8346,13 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B339" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C339" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="D339" t="s">
         <v>85</v>
@@ -8338,16 +8363,16 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B340" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C340" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="D340" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="E340" t="s">
         <v>10</v>
@@ -8355,16 +8380,16 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B341" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C341" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="D341" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="E341" t="s">
         <v>37</v>
@@ -8372,16 +8397,16 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B342" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C342" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="D342" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="E342" t="s">
         <v>10</v>
@@ -8389,13 +8414,13 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B343" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C343" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="D343" t="s">
         <v>28</v>
@@ -8406,13 +8431,13 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B344" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="D344" t="s">
         <v>27</v>
@@ -8423,13 +8448,13 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B345" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C345" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="D345" t="s">
         <v>83</v>
@@ -8440,13 +8465,13 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B346" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D346" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="E346" t="s">
         <v>14</v>
@@ -8454,13 +8479,13 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B347" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D347" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="E347" t="s">
         <v>10</v>
@@ -8468,16 +8493,16 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B348" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C348" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="D348" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="E348" t="s">
         <v>10</v>
@@ -8485,16 +8510,16 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B349" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C349" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="D349" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="E349" t="s">
         <v>10</v>
@@ -8502,138 +8527,138 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B350" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C350" t="s">
         <v>241</v>
       </c>
       <c r="D350" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="E350" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="F350" t="s">
         <v>8</v>
       </c>
       <c r="H350" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B351" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C351" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="D351" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="E351" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B352" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C352" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="D352" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="E352" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B353" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C353" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="D353" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="E353" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B354" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C354" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="D354" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="E354" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B355" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C355" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="D355" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="E355" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B356" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C356" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="D356" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="E356" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B357" t="s">
+        <v>420</v>
+      </c>
+      <c r="D357" t="s">
         <v>435</v>
-      </c>
-      <c r="D357" t="s">
-        <v>450</v>
       </c>
       <c r="E357" t="s">
         <v>37</v>
@@ -8641,218 +8666,218 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B358" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D358" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="E358" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B359" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D359" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="E359" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B360" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D360" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="E360" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B361" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D361" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="E361" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B362" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D362" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="E362" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B363" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D363" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="E363" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B364" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D364" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="E364" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B365" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D365" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="E365" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
+        <v>504</v>
+      </c>
+      <c r="B366" t="s">
+        <v>420</v>
+      </c>
+      <c r="C366" t="s">
         <v>519</v>
       </c>
-      <c r="B366" t="s">
-        <v>435</v>
-      </c>
-      <c r="C366" t="s">
-        <v>534</v>
-      </c>
       <c r="D366" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="E366" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B367" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C367" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="D367" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="E367" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B368" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D368" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="E368" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B369" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D369" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="E369" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B370" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D370" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="E370" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B371" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D371" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="E371" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B372" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C372" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="D372" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="E372" t="s">
         <v>37</v>
@@ -8860,27 +8885,27 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B373" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D373" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="E373" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B374" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D374" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="E374" t="s">
         <v>37</v>
@@ -8888,13 +8913,13 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B375" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D375" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="E375" t="s">
         <v>17</v>
@@ -8902,524 +8927,524 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B376" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D376" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="E376" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B377" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D377" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="E377" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B378" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D378" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="E378" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B379" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D379" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="E379" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B380" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D380" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="E380" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B381" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D381" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="E381" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B382" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D382" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="E382" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B383" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D383" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="E383" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B384" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D384" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="E384" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B385" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D385" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="E385" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B386" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D386" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="E386" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B387" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D387" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="E387" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B388" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D388" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="E388" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B389" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D389" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="E389" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B390" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D390" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="E390" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B391" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D391" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="E391" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B392" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D392" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="E392" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B393" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D393" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="E393" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B394" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C394" t="s">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="D394" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="E394" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B395" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D395" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="E395" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B396" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D396" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="E396" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B397" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D397" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="E397" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B398" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D398" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="E398" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B399" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D399" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="E399" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B400" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D400" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="E400" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B401" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D401" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="E401" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B402" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D402" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="E402" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B403" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C403" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="D403" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="E403" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B404" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D404" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="E404" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B405" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C405" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="D405" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="E405" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="I405" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B406" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C406" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="D406" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="E406" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B407" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D407" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="E407" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B408" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C408" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="D408" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="E408" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B409" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C409" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="D409" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="E409" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B410" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D410" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="E410" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B411" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D411" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="E411" t="s">
         <v>17</v>
@@ -9427,24 +9452,24 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B412" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D412" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="E412" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B413" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C413" t="s">
         <v>242</v>
@@ -9458,138 +9483,138 @@
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B414" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C414" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="D414" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="E414" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B415" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C415" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="D415" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="E415" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B416" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C416" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="D416" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="E416" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B417" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C417" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="D417" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E417" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B418" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C418" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="D418" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="E418" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B419" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D419" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="E419" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B420" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C420" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="D420" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="E420" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="F420" t="s">
         <v>8</v>
       </c>
       <c r="H420" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B421" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C421" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
       <c r="D421" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="E421" t="s">
         <v>17</v>
@@ -9598,21 +9623,21 @@
         <v>8</v>
       </c>
       <c r="H421" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B422" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C422" t="s">
-        <v>634</v>
+        <v>619</v>
       </c>
       <c r="D422" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="E422" t="s">
         <v>17</v>
@@ -9621,1114 +9646,1114 @@
         <v>8</v>
       </c>
       <c r="H422" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B423" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C423" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="D423" t="s">
         <v>54</v>
       </c>
       <c r="E423" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B424" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C424" t="s">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="D424" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="E424" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B425" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C425" t="s">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="D425" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="E425" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B426" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C426" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="D426" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="E426" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B427" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C427" t="s">
-        <v>639</v>
+        <v>624</v>
       </c>
       <c r="D427" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="E427" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B428" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C428" t="s">
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="D428" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="E428" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B429" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C429" t="s">
-        <v>641</v>
+        <v>626</v>
       </c>
       <c r="D429" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="E429" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B430" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C430" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="D430" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="E430" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B431" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C431" t="s">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="D431" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="E431" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B432" t="s">
+        <v>523</v>
+      </c>
+      <c r="C432" t="s">
+        <v>629</v>
+      </c>
+      <c r="D432" t="s">
+        <v>537</v>
+      </c>
+      <c r="E432" t="s">
         <v>538</v>
-      </c>
-      <c r="C432" t="s">
-        <v>644</v>
-      </c>
-      <c r="D432" t="s">
-        <v>552</v>
-      </c>
-      <c r="E432" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B433" t="s">
+        <v>523</v>
+      </c>
+      <c r="C433" t="s">
+        <v>630</v>
+      </c>
+      <c r="D433" t="s">
+        <v>539</v>
+      </c>
+      <c r="E433" t="s">
         <v>538</v>
-      </c>
-      <c r="C433" t="s">
-        <v>645</v>
-      </c>
-      <c r="D433" t="s">
-        <v>554</v>
-      </c>
-      <c r="E433" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B434" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D434" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="E434" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B435" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C435" t="s">
         <v>105</v>
       </c>
       <c r="D435" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="E435" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B436" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D436" t="s">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="E436" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
+        <v>616</v>
+      </c>
+      <c r="B437" t="s">
+        <v>523</v>
+      </c>
+      <c r="C437" t="s">
         <v>631</v>
       </c>
-      <c r="B437" t="s">
-        <v>538</v>
-      </c>
-      <c r="C437" t="s">
-        <v>646</v>
-      </c>
       <c r="D437" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="E437" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B438" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C438" t="s">
-        <v>647</v>
+        <v>632</v>
       </c>
       <c r="D438" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="E438" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B439" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C439" t="s">
-        <v>648</v>
+        <v>633</v>
       </c>
       <c r="D439" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="E439" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B440" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C440" t="s">
-        <v>649</v>
+        <v>634</v>
       </c>
       <c r="D440" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="E440" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B441" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D441" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="E441" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B442" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D442" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="E442" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B443" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D443" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="E443" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B444" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D444" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="E444" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B445" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D445" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="E445" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B446" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D446" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="E446" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B447" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D447" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="E447" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B448" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D448" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="E448" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B449" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D449" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="E449" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B450" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D450" t="s">
-        <v>575</v>
+        <v>560</v>
       </c>
       <c r="E450" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B451" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D451" t="s">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="E451" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B452" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D452" t="s">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="E452" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B453" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D453" t="s">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="E453" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B454" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D454" t="s">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="E454" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B455" t="s">
+        <v>523</v>
+      </c>
+      <c r="D455" t="s">
+        <v>566</v>
+      </c>
+      <c r="E455" t="s">
         <v>538</v>
-      </c>
-      <c r="D455" t="s">
-        <v>581</v>
-      </c>
-      <c r="E455" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B456" t="s">
+        <v>523</v>
+      </c>
+      <c r="D456" t="s">
+        <v>567</v>
+      </c>
+      <c r="E456" t="s">
         <v>538</v>
-      </c>
-      <c r="D456" t="s">
-        <v>582</v>
-      </c>
-      <c r="E456" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B457" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D457" t="s">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="E457" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B458" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D458" t="s">
-        <v>584</v>
+        <v>569</v>
       </c>
       <c r="E458" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B459" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D459" t="s">
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="E459" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B460" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D460" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="E460" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B461" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D461" t="s">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="E461" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B462" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C462" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="D462" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="E462" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B463" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C463" t="s">
-        <v>651</v>
+        <v>636</v>
       </c>
       <c r="D463" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="E463" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B464" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D464" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="E464" t="s">
-        <v>591</v>
+        <v>576</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B465" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D465" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="E465" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B466" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C466" t="s">
-        <v>652</v>
+        <v>637</v>
       </c>
       <c r="D466" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="E466" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B467" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C467" t="s">
-        <v>653</v>
+        <v>638</v>
       </c>
       <c r="D467" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="E467" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B468" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D468" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="E468" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B469" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D469" t="s">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="E469" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B470" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D470" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="E470" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B471" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D471" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="E471" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B472" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D472" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="E472" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B473" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D473" t="s">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="E473" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B474" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D474" t="s">
-        <v>602</v>
+        <v>587</v>
       </c>
       <c r="E474" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B475" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D475" t="s">
-        <v>603</v>
+        <v>588</v>
       </c>
       <c r="E475" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B476" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D476" t="s">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="E476" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B477" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D477" t="s">
-        <v>605</v>
+        <v>590</v>
       </c>
       <c r="E477" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B478" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D478" t="s">
-        <v>606</v>
+        <v>591</v>
       </c>
       <c r="E478" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B479" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D479" t="s">
-        <v>607</v>
+        <v>592</v>
       </c>
       <c r="E479" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B480" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D480" t="s">
-        <v>608</v>
+        <v>593</v>
       </c>
       <c r="E480" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B481" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D481" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
       <c r="E481" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B482" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D482" t="s">
-        <v>610</v>
+        <v>595</v>
       </c>
       <c r="E482" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B483" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D483" t="s">
-        <v>611</v>
+        <v>596</v>
       </c>
       <c r="E483" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B484" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D484" t="s">
-        <v>612</v>
+        <v>597</v>
       </c>
       <c r="E484" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B485" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D485" t="s">
-        <v>613</v>
+        <v>598</v>
       </c>
       <c r="E485" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B486" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D486" t="s">
-        <v>614</v>
+        <v>599</v>
       </c>
       <c r="E486" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B487" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D487" t="s">
-        <v>615</v>
+        <v>600</v>
       </c>
       <c r="E487" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B488" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D488" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="E488" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B489" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D489" t="s">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="E489" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B490" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D490" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="E490" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B491" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D491" t="s">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="E491" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B492" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D492" t="s">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="E492" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B493" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D493" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="E493" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B494" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D494" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="E494" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B495" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D495" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="E495" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B496" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D496" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="E496" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B497" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D497" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="E497" t="s">
         <v>37</v>
@@ -10736,58 +10761,58 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B498" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D498" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="E498" t="s">
-        <v>627</v>
+        <v>612</v>
       </c>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B499" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D499" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="E499" t="s">
         <v>9</v>
       </c>
       <c r="H499" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B500" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D500" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="E500" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="B501" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D501" t="s">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="E501" t="s">
         <v>18</v>
